--- a/已调研对接仪器清单(1).xlsx
+++ b/已调研对接仪器清单(1).xlsx
@@ -2358,7 +2358,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2378,13 +2378,6 @@
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10.5"/>
@@ -3092,13 +3085,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3107,118 +3103,115 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3259,10 +3252,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3283,7 +3276,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3334,16 +3327,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3376,34 +3369,34 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
@@ -3461,17 +3454,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -11896,22 +11879,22 @@
     <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A190">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A101:A102">
     <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A161:A170">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A183:A189">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A201:A205">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A206:A210">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A220:A235">
     <cfRule type="duplicateValues" dxfId="0" priority="10"/>
